--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2019_biobio_provincial.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2019_biobio_provincial.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Arauco</t>
   </si>
   <si>
-    <t xml:space="preserve">Bíobío</t>
+    <t xml:space="preserve">Bío-Bío</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 00:33</t>
+    <t xml:space="preserve">2026-10-05 05:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Biobio</t>
+    <t xml:space="preserve">Region de Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
